--- a/Master/2025_and_2026/SSS2.xlsx
+++ b/Master/2025_and_2026/SSS2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Reporter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Reporter\Master\2025_and_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D2B83E-0363-4192-968D-197976F7D6D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07282501-1C6F-4328-ADFF-944CF88C3790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{52FCD3C7-9332-4CF4-B3EE-1A8AB54D36C0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="83">
   <si>
     <t>admission_no</t>
   </si>
@@ -244,6 +244,36 @@
   </si>
   <si>
     <t>Geography</t>
+  </si>
+  <si>
+    <t>department</t>
+  </si>
+  <si>
+    <t>Science</t>
+  </si>
+  <si>
+    <t>phone_number</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>+2348090650910</t>
+  </si>
+  <si>
+    <t>saddy344@gmail.com</t>
+  </si>
+  <si>
+    <t>saddyand myles@gmail.com</t>
+  </si>
+  <si>
+    <t>saddy@gmail.com</t>
+  </si>
+  <si>
+    <t>saddy124@gmail.com</t>
+  </si>
+  <si>
+    <t>Art</t>
   </si>
 </sst>
 </file>
@@ -613,35 +643,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0FA66E3-6DED-4387-8FC0-615D1610DC2E}">
-  <dimension ref="A1:AL10"/>
+  <dimension ref="A1:AO10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="13" width="13.90625" customWidth="1"/>
-    <col min="14" max="14" width="19.54296875" customWidth="1"/>
-    <col min="15" max="15" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.36328125" customWidth="1"/>
-    <col min="17" max="17" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="21.08984375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="24.7265625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="13.90625" customWidth="1"/>
+    <col min="17" max="17" width="19.54296875" customWidth="1"/>
+    <col min="18" max="18" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.36328125" customWidth="1"/>
+    <col min="20" max="20" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.08984375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="10" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="12" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:41" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -664,100 +697,109 @@
         <v>40</v>
       </c>
       <c r="H1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K1" t="s">
         <v>42</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>43</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>47</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>44</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>48</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>49</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>6</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>12</v>
       </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
         <v>7</v>
       </c>
-      <c r="T1" t="s">
+      <c r="W1" t="s">
         <v>13</v>
       </c>
-      <c r="U1" t="s">
+      <c r="X1" t="s">
         <v>14</v>
       </c>
-      <c r="V1" t="s">
+      <c r="Y1" t="s">
         <v>15</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Z1" t="s">
         <v>8</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AA1" t="s">
         <v>9</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AB1" t="s">
         <v>10</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AC1" t="s">
         <v>11</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AD1" t="s">
         <v>16</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AE1" t="s">
         <v>17</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AF1" t="s">
         <v>18</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AG1" t="s">
         <v>19</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AH1" t="s">
         <v>20</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AI1" t="s">
         <v>21</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AJ1" t="s">
         <v>22</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AK1" t="s">
         <v>23</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AL1" t="s">
         <v>24</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AM1" t="s">
         <v>25</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AN1" t="s">
         <v>26</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AO1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>27101</v>
       </c>
@@ -780,57 +822,66 @@
         <v>41</v>
       </c>
       <c r="H2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K2" t="s">
         <v>50</v>
       </c>
-      <c r="I2" t="s">
+      <c r="L2" t="s">
         <v>51</v>
       </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>52</v>
       </c>
-      <c r="K2" s="3">
+      <c r="N2" s="3">
         <v>37904</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1">
-        <v>1</v>
-      </c>
-      <c r="P2" s="1"/>
-      <c r="Q2">
-        <v>1</v>
-      </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="S2">
-        <v>1</v>
-      </c>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1">
+        <v>1</v>
+      </c>
+      <c r="S2" s="1"/>
       <c r="T2">
         <v>1</v>
       </c>
+      <c r="U2">
+        <v>1</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
       <c r="W2">
         <v>1</v>
       </c>
-      <c r="Y2">
-        <v>1</v>
-      </c>
-      <c r="AC2">
-        <v>1</v>
-      </c>
-      <c r="AE2">
+      <c r="Z2">
+        <v>1</v>
+      </c>
+      <c r="AB2">
         <v>1</v>
       </c>
       <c r="AF2">
         <v>1</v>
       </c>
+      <c r="AH2">
+        <v>1</v>
+      </c>
+      <c r="AI2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>27102</v>
       </c>
@@ -853,57 +904,66 @@
         <v>41</v>
       </c>
       <c r="H3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" t="s">
         <v>45</v>
       </c>
-      <c r="I3" t="s">
+      <c r="L3" t="s">
         <v>51</v>
       </c>
-      <c r="J3" t="s">
+      <c r="M3" t="s">
         <v>55</v>
       </c>
-      <c r="K3" s="3">
+      <c r="N3" s="3">
         <v>37691</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1">
-        <v>1</v>
-      </c>
-      <c r="P3" s="1"/>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="S3">
-        <v>1</v>
-      </c>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1">
+        <v>1</v>
+      </c>
+      <c r="S3" s="1"/>
       <c r="T3">
         <v>1</v>
       </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3">
+        <v>1</v>
+      </c>
       <c r="W3">
         <v>1</v>
       </c>
-      <c r="Y3">
-        <v>1</v>
-      </c>
-      <c r="AC3">
-        <v>1</v>
-      </c>
-      <c r="AE3">
+      <c r="Z3">
+        <v>1</v>
+      </c>
+      <c r="AB3">
         <v>1</v>
       </c>
       <c r="AF3">
         <v>1</v>
       </c>
+      <c r="AH3">
+        <v>1</v>
+      </c>
+      <c r="AI3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>27103</v>
       </c>
@@ -926,57 +986,66 @@
         <v>41</v>
       </c>
       <c r="H4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J4" t="s">
+        <v>80</v>
+      </c>
+      <c r="K4" t="s">
         <v>45</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>51</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>58</v>
       </c>
-      <c r="K4" s="3">
+      <c r="N4" s="3">
         <v>37967</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1">
-        <v>1</v>
-      </c>
-      <c r="P4" s="1"/>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <v>1</v>
-      </c>
-      <c r="S4">
-        <v>1</v>
-      </c>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1">
+        <v>1</v>
+      </c>
+      <c r="S4" s="1"/>
       <c r="T4">
         <v>1</v>
       </c>
+      <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
       <c r="W4">
         <v>1</v>
       </c>
-      <c r="Y4">
-        <v>1</v>
-      </c>
-      <c r="AC4">
-        <v>1</v>
-      </c>
-      <c r="AE4">
+      <c r="Z4">
+        <v>1</v>
+      </c>
+      <c r="AB4">
         <v>1</v>
       </c>
       <c r="AF4">
         <v>1</v>
       </c>
+      <c r="AH4">
+        <v>1</v>
+      </c>
+      <c r="AI4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>27104</v>
       </c>
@@ -999,57 +1068,66 @@
         <v>41</v>
       </c>
       <c r="H5" t="s">
+        <v>82</v>
+      </c>
+      <c r="I5" t="s">
+        <v>77</v>
+      </c>
+      <c r="J5" t="s">
+        <v>81</v>
+      </c>
+      <c r="K5" t="s">
         <v>45</v>
       </c>
-      <c r="I5" t="s">
+      <c r="L5" t="s">
         <v>51</v>
       </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
         <v>61</v>
       </c>
-      <c r="K5" s="3">
+      <c r="N5" s="3">
         <v>37665</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="O5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1">
-        <v>1</v>
-      </c>
-      <c r="P5" s="1"/>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>1</v>
-      </c>
-      <c r="S5">
-        <v>1</v>
-      </c>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1">
+        <v>1</v>
+      </c>
+      <c r="S5" s="1"/>
       <c r="T5">
         <v>1</v>
       </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
       <c r="W5">
         <v>1</v>
       </c>
-      <c r="Y5">
-        <v>1</v>
-      </c>
       <c r="Z5">
         <v>1</v>
       </c>
+      <c r="AB5">
+        <v>1</v>
+      </c>
       <c r="AC5">
         <v>1</v>
       </c>
       <c r="AF5">
         <v>1</v>
       </c>
+      <c r="AI5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>27105</v>
       </c>
@@ -1072,57 +1150,66 @@
         <v>41</v>
       </c>
       <c r="H6" t="s">
+        <v>82</v>
+      </c>
+      <c r="I6" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" t="s">
+        <v>80</v>
+      </c>
+      <c r="K6" t="s">
         <v>45</v>
       </c>
-      <c r="I6" t="s">
+      <c r="L6" t="s">
         <v>51</v>
       </c>
-      <c r="J6" t="s">
+      <c r="M6" t="s">
         <v>64</v>
       </c>
-      <c r="K6" s="3">
+      <c r="N6" s="3">
         <v>37755</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="O6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="P6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1">
-        <v>1</v>
-      </c>
-      <c r="P6" s="1"/>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>1</v>
-      </c>
-      <c r="S6">
-        <v>1</v>
-      </c>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1">
+        <v>1</v>
+      </c>
+      <c r="S6" s="1"/>
       <c r="T6">
         <v>1</v>
       </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
       <c r="W6">
         <v>1</v>
       </c>
-      <c r="Y6">
-        <v>1</v>
-      </c>
-      <c r="AC6">
-        <v>1</v>
-      </c>
-      <c r="AE6">
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
         <v>1</v>
       </c>
       <c r="AF6">
         <v>1</v>
       </c>
+      <c r="AH6">
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>27106</v>
       </c>
@@ -1145,57 +1232,66 @@
         <v>41</v>
       </c>
       <c r="H7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K7" t="s">
         <v>45</v>
       </c>
-      <c r="I7" t="s">
+      <c r="L7" t="s">
         <v>51</v>
       </c>
-      <c r="J7" t="s">
+      <c r="M7" t="s">
         <v>66</v>
       </c>
-      <c r="K7" s="3">
+      <c r="N7" s="3">
         <v>37636</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="O7" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="P7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1">
-        <v>1</v>
-      </c>
-      <c r="P7" s="1"/>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>1</v>
-      </c>
-      <c r="S7">
-        <v>1</v>
-      </c>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1">
+        <v>1</v>
+      </c>
+      <c r="S7" s="1"/>
       <c r="T7">
         <v>1</v>
       </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
-      <c r="Y7">
-        <v>1</v>
-      </c>
-      <c r="AC7">
-        <v>1</v>
-      </c>
-      <c r="AE7">
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
         <v>1</v>
       </c>
       <c r="AF7">
         <v>1</v>
       </c>
+      <c r="AH7">
+        <v>1</v>
+      </c>
+      <c r="AI7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>27107</v>
       </c>
@@ -1218,57 +1314,66 @@
         <v>41</v>
       </c>
       <c r="H8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s">
+        <v>77</v>
+      </c>
+      <c r="J8" t="s">
+        <v>80</v>
+      </c>
+      <c r="K8" t="s">
         <v>45</v>
       </c>
-      <c r="I8" t="s">
+      <c r="L8" t="s">
         <v>51</v>
       </c>
-      <c r="J8" t="s">
+      <c r="M8" t="s">
         <v>68</v>
       </c>
-      <c r="K8" s="3">
+      <c r="N8" s="3">
         <v>37880</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="O8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="P8" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1">
-        <v>1</v>
-      </c>
-      <c r="P8" s="1"/>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
-      </c>
-      <c r="S8">
-        <v>1</v>
-      </c>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1">
+        <v>1</v>
+      </c>
+      <c r="S8" s="1"/>
       <c r="T8">
         <v>1</v>
       </c>
-      <c r="X8">
-        <v>1</v>
-      </c>
-      <c r="Y8">
-        <v>1</v>
-      </c>
-      <c r="AC8">
-        <v>1</v>
-      </c>
-      <c r="AE8">
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
         <v>1</v>
       </c>
       <c r="AF8">
         <v>1</v>
       </c>
+      <c r="AH8">
+        <v>1</v>
+      </c>
+      <c r="AI8">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>27108</v>
       </c>
@@ -1291,57 +1396,66 @@
         <v>41</v>
       </c>
       <c r="H9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s">
+        <v>77</v>
+      </c>
+      <c r="J9" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" t="s">
         <v>45</v>
       </c>
-      <c r="I9" t="s">
+      <c r="L9" t="s">
         <v>51</v>
       </c>
-      <c r="J9" t="s">
+      <c r="M9" t="s">
         <v>70</v>
       </c>
-      <c r="K9" s="3">
+      <c r="N9" s="3">
         <v>37850</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="O9" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="P9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1">
-        <v>1</v>
-      </c>
-      <c r="P9" s="1"/>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9">
-        <v>1</v>
-      </c>
-      <c r="S9">
-        <v>1</v>
-      </c>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1">
+        <v>1</v>
+      </c>
+      <c r="S9" s="1"/>
       <c r="T9">
         <v>1</v>
       </c>
-      <c r="X9">
-        <v>1</v>
-      </c>
-      <c r="Y9">
-        <v>1</v>
-      </c>
-      <c r="AC9">
-        <v>1</v>
-      </c>
-      <c r="AE9">
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
         <v>1</v>
       </c>
       <c r="AF9">
         <v>1</v>
       </c>
+      <c r="AH9">
+        <v>1</v>
+      </c>
+      <c r="AI9">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>27109</v>
       </c>
@@ -1364,53 +1478,62 @@
         <v>41</v>
       </c>
       <c r="H10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J10" t="s">
+        <v>80</v>
+      </c>
+      <c r="K10" t="s">
         <v>45</v>
       </c>
-      <c r="I10" t="s">
+      <c r="L10" t="s">
         <v>51</v>
       </c>
-      <c r="J10" t="s">
+      <c r="M10" t="s">
         <v>70</v>
       </c>
-      <c r="K10" s="3">
+      <c r="N10" s="3">
         <v>37851</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="O10" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="P10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1">
-        <v>1</v>
-      </c>
-      <c r="P10" s="1"/>
-      <c r="Q10">
-        <v>1</v>
-      </c>
-      <c r="R10">
-        <v>1</v>
-      </c>
-      <c r="S10">
-        <v>1</v>
-      </c>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1">
+        <v>1</v>
+      </c>
+      <c r="S10" s="1"/>
       <c r="T10">
         <v>1</v>
       </c>
-      <c r="X10">
-        <v>1</v>
-      </c>
-      <c r="Y10">
-        <v>1</v>
-      </c>
-      <c r="AC10">
-        <v>1</v>
-      </c>
-      <c r="AE10">
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+      <c r="AB10">
         <v>1</v>
       </c>
       <c r="AF10">
+        <v>1</v>
+      </c>
+      <c r="AH10">
+        <v>1</v>
+      </c>
+      <c r="AI10">
         <v>1</v>
       </c>
     </row>
